--- a/riobamba-censo-data/shp/plataforma_enie.xlsx
+++ b/riobamba-censo-data/shp/plataforma_enie.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -498,11 +498,12 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,25 +534,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>edad0_14</t>
+          <t>edad0_4</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>edad15_29</t>
+          <t>edad5_11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>edad30_44</t>
+          <t>edad12_17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>edad45_64</t>
+          <t>edad18_29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>edad30_64</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>edad65mas</t>
         </is>
@@ -578,18 +584,21 @@
         <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J2" t="n">
+        <v>56</v>
+      </c>
+      <c r="K2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -614,18 +623,21 @@
         <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>7</v>
       </c>
-      <c r="I3" t="n">
-        <v>15</v>
-      </c>
       <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="n">
         <v>14</v>
       </c>
     </row>
@@ -650,18 +662,21 @@
         <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -686,18 +701,21 @@
         <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="n">
-        <v>22</v>
-      </c>
       <c r="J5" t="n">
+        <v>34</v>
+      </c>
+      <c r="K5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -722,18 +740,21 @@
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
+        <v>31</v>
+      </c>
+      <c r="K6" t="n">
         <v>12</v>
       </c>
     </row>
@@ -758,18 +779,21 @@
         <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="n">
         <v>7</v>
       </c>
     </row>
@@ -794,18 +818,21 @@
         <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
+        <v>58</v>
+      </c>
+      <c r="K8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -830,18 +857,21 @@
         <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>32</v>
       </c>
       <c r="J9" t="n">
+        <v>51</v>
+      </c>
+      <c r="K9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -866,18 +896,21 @@
         <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J10" t="n">
+        <v>67</v>
+      </c>
+      <c r="K10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -902,18 +935,21 @@
         <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
+        <v>27</v>
+      </c>
+      <c r="K11" t="n">
         <v>14</v>
       </c>
     </row>
@@ -938,18 +974,21 @@
         <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
       </c>
     </row>
@@ -974,18 +1013,21 @@
         <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>16</v>
+      </c>
+      <c r="J13" t="n">
         <v>24</v>
       </c>
-      <c r="H13" t="n">
-        <v>13</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1010,18 +1052,21 @@
         <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K14" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1046,18 +1091,21 @@
         <v>34</v>
       </c>
       <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>10</v>
       </c>
-      <c r="G15" t="n">
-        <v>12</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
+        <v>27</v>
+      </c>
+      <c r="K15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1082,18 +1130,21 @@
         <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
+        <v>39</v>
+      </c>
+      <c r="K16" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1121,15 +1172,18 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1154,18 +1208,21 @@
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
+        <v>30</v>
+      </c>
+      <c r="K18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1190,18 +1247,21 @@
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1226,18 +1286,21 @@
         <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>8</v>
       </c>
       <c r="J20" t="n">
+        <v>18</v>
+      </c>
+      <c r="K20" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1262,18 +1325,21 @@
         <v>41</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
+        <v>37</v>
+      </c>
+      <c r="K21" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1298,18 +1364,21 @@
         <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H22" t="n">
+        <v>9</v>
+      </c>
+      <c r="I22" t="n">
         <v>14</v>
       </c>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
       <c r="J22" t="n">
+        <v>35</v>
+      </c>
+      <c r="K22" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1334,18 +1403,21 @@
         <v>46</v>
       </c>
       <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
         <v>9</v>
       </c>
-      <c r="G23" t="n">
-        <v>29</v>
-      </c>
-      <c r="H23" t="n">
-        <v>17</v>
-      </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
+        <v>43</v>
+      </c>
+      <c r="K23" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1370,18 +1442,21 @@
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
+        <v>22</v>
+      </c>
+      <c r="K24" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1406,18 +1481,21 @@
         <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J25" t="n">
+        <v>27</v>
+      </c>
+      <c r="K25" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1442,18 +1520,21 @@
         <v>126</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="H26" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="I26" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="J26" t="n">
+        <v>106</v>
+      </c>
+      <c r="K26" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1478,18 +1559,21 @@
         <v>112</v>
       </c>
       <c r="F27" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="H27" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J27" t="n">
+        <v>79</v>
+      </c>
+      <c r="K27" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1514,18 +1598,21 @@
         <v>54</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
+        <v>43</v>
+      </c>
+      <c r="K28" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1550,18 +1637,21 @@
         <v>27</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
+        <v>28</v>
+      </c>
+      <c r="K29" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1586,18 +1676,21 @@
         <v>56</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G30" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
+        <v>57</v>
+      </c>
+      <c r="K30" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1622,18 +1715,21 @@
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
+        <v>14</v>
+      </c>
+      <c r="K31" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1658,18 +1754,21 @@
         <v>32</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J32" t="n">
+        <v>39</v>
+      </c>
+      <c r="K32" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1694,18 +1793,21 @@
         <v>24</v>
       </c>
       <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>9</v>
       </c>
-      <c r="G33" t="n">
-        <v>9</v>
-      </c>
-      <c r="H33" t="n">
-        <v>9</v>
-      </c>
-      <c r="I33" t="n">
-        <v>10</v>
-      </c>
       <c r="J33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K33" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1730,18 +1832,21 @@
         <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="n">
-        <v>3</v>
-      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
+        <v>4</v>
+      </c>
+      <c r="K34" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1766,18 +1871,21 @@
         <v>95</v>
       </c>
       <c r="F35" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="H35" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="I35" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J35" t="n">
+        <v>70</v>
+      </c>
+      <c r="K35" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1802,18 +1910,21 @@
         <v>45</v>
       </c>
       <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
         <v>10</v>
       </c>
-      <c r="G36" t="n">
-        <v>17</v>
-      </c>
-      <c r="H36" t="n">
-        <v>16</v>
-      </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J36" t="n">
+        <v>31</v>
+      </c>
+      <c r="K36" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1838,18 +1949,21 @@
         <v>46</v>
       </c>
       <c r="F37" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
+        <v>40</v>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1874,18 +1988,21 @@
         <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
+        <v>37</v>
+      </c>
+      <c r="K38" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1910,18 +2027,21 @@
         <v>31</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J39" t="n">
+        <v>32</v>
+      </c>
+      <c r="K39" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1946,18 +2066,21 @@
         <v>23</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>8</v>
       </c>
-      <c r="H40" t="n">
-        <v>9</v>
-      </c>
-      <c r="I40" t="n">
-        <v>10</v>
-      </c>
       <c r="J40" t="n">
+        <v>19</v>
+      </c>
+      <c r="K40" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1982,18 +2105,21 @@
         <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
         <v>18</v>
       </c>
       <c r="J41" t="n">
+        <v>42</v>
+      </c>
+      <c r="K41" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2018,18 +2144,21 @@
         <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
+        <v>26</v>
+      </c>
+      <c r="K42" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2054,18 +2183,21 @@
         <v>35</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J43" t="n">
+        <v>28</v>
+      </c>
+      <c r="K43" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2090,18 +2222,21 @@
         <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H44" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
+        <v>46</v>
+      </c>
+      <c r="K44" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2126,18 +2261,21 @@
         <v>8</v>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
       <c r="J45" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2162,18 +2300,21 @@
         <v>147</v>
       </c>
       <c r="F46" t="n">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="G46" t="n">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="H46" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="I46" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J46" t="n">
+        <v>118</v>
+      </c>
+      <c r="K46" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2198,18 +2339,21 @@
         <v>119</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="H47" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I47" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J47" t="n">
+        <v>88</v>
+      </c>
+      <c r="K47" t="n">
         <v>27</v>
       </c>
     </row>
@@ -2234,18 +2378,21 @@
         <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
+        <v>34</v>
+      </c>
+      <c r="K48" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2270,18 +2417,21 @@
         <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H49" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
+        <v>42</v>
+      </c>
+      <c r="K49" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2306,18 +2456,21 @@
         <v>21</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I50" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
+        <v>24</v>
+      </c>
+      <c r="K50" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2342,18 +2495,21 @@
         <v>62</v>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H51" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
+        <v>47</v>
+      </c>
+      <c r="K51" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2378,18 +2534,21 @@
         <v>47</v>
       </c>
       <c r="F52" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I52" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
+        <v>45</v>
+      </c>
+      <c r="K52" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2414,18 +2573,21 @@
         <v>34</v>
       </c>
       <c r="F53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H53" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I53" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J53" t="n">
+        <v>22</v>
+      </c>
+      <c r="K53" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2450,18 +2612,21 @@
         <v>61</v>
       </c>
       <c r="F54" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H54" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
+        <v>48</v>
+      </c>
+      <c r="K54" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2486,18 +2651,21 @@
         <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H55" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J55" t="n">
+        <v>34</v>
+      </c>
+      <c r="K55" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2522,18 +2690,21 @@
         <v>33</v>
       </c>
       <c r="F56" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J56" t="n">
+        <v>32</v>
+      </c>
+      <c r="K56" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2558,18 +2729,21 @@
         <v>48</v>
       </c>
       <c r="F57" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J57" t="n">
+        <v>33</v>
+      </c>
+      <c r="K57" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2594,18 +2768,21 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G58" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J58" t="n">
+        <v>29</v>
+      </c>
+      <c r="K58" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2630,18 +2807,21 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H59" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J59" t="n">
+        <v>40</v>
+      </c>
+      <c r="K59" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2666,18 +2846,21 @@
         <v>58</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H60" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
+        <v>43</v>
+      </c>
+      <c r="K60" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2702,18 +2885,21 @@
         <v>46</v>
       </c>
       <c r="F61" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J61" t="n">
+        <v>36</v>
+      </c>
+      <c r="K61" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2738,18 +2924,21 @@
         <v>8</v>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
+        <v>12</v>
+      </c>
+      <c r="K62" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2774,18 +2963,21 @@
         <v>3</v>
       </c>
       <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" t="n">
-        <v>3</v>
-      </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>2</v>
       </c>
       <c r="J63" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2810,18 +3002,21 @@
         <v>33</v>
       </c>
       <c r="F64" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H64" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
+        <v>23</v>
+      </c>
+      <c r="K64" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2846,18 +3041,21 @@
         <v>16</v>
       </c>
       <c r="F65" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="n">
-        <v>8</v>
-      </c>
-      <c r="I65" t="n">
-        <v>9</v>
-      </c>
       <c r="J65" t="n">
+        <v>17</v>
+      </c>
+      <c r="K65" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2882,18 +3080,21 @@
         <v>40</v>
       </c>
       <c r="F66" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H66" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J66" t="n">
+        <v>28</v>
+      </c>
+      <c r="K66" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2918,18 +3119,21 @@
         <v>20</v>
       </c>
       <c r="F67" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J67" t="n">
+        <v>12</v>
+      </c>
+      <c r="K67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2954,18 +3158,21 @@
         <v>33</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H68" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J68" t="n">
+        <v>28</v>
+      </c>
+      <c r="K68" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2990,18 +3197,21 @@
         <v>41</v>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H69" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
+        <v>31</v>
+      </c>
+      <c r="K69" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3026,18 +3236,21 @@
         <v>29</v>
       </c>
       <c r="F70" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J70" t="n">
+        <v>28</v>
+      </c>
+      <c r="K70" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3062,18 +3275,21 @@
         <v>61</v>
       </c>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H71" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J71" t="n">
+        <v>49</v>
+      </c>
+      <c r="K71" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3098,18 +3314,21 @@
         <v>22</v>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J72" t="n">
+        <v>23</v>
+      </c>
+      <c r="K72" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3134,18 +3353,21 @@
         <v>46</v>
       </c>
       <c r="F73" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G73" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H73" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J73" t="n">
+        <v>33</v>
+      </c>
+      <c r="K73" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3170,18 +3392,21 @@
         <v>75</v>
       </c>
       <c r="F74" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G74" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H74" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J74" t="n">
+        <v>52</v>
+      </c>
+      <c r="K74" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3206,18 +3431,21 @@
         <v>246</v>
       </c>
       <c r="F75" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="H75" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="I75" t="n">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="J75" t="n">
+        <v>192</v>
+      </c>
+      <c r="K75" t="n">
         <v>66</v>
       </c>
     </row>
@@ -3242,18 +3470,21 @@
         <v>32</v>
       </c>
       <c r="F76" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J76" t="n">
+        <v>30</v>
+      </c>
+      <c r="K76" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3278,18 +3509,21 @@
         <v>77</v>
       </c>
       <c r="F77" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G77" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H77" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
+        <v>62</v>
+      </c>
+      <c r="K77" t="n">
         <v>29</v>
       </c>
     </row>
@@ -3314,18 +3548,21 @@
         <v>66</v>
       </c>
       <c r="F78" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="H78" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I78" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
+        <v>65</v>
+      </c>
+      <c r="K78" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3350,18 +3587,21 @@
         <v>44</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H79" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
+        <v>43</v>
+      </c>
+      <c r="K79" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3386,18 +3626,21 @@
         <v>62</v>
       </c>
       <c r="F80" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G80" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H80" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
+        <v>51</v>
+      </c>
+      <c r="K80" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3422,18 +3665,21 @@
         <v>21</v>
       </c>
       <c r="F81" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
         <v>6</v>
       </c>
       <c r="H81" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
+        <v>18</v>
+      </c>
+      <c r="K81" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3458,18 +3704,21 @@
         <v>63</v>
       </c>
       <c r="F82" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H82" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I82" t="n">
         <v>23</v>
       </c>
       <c r="J82" t="n">
+        <v>54</v>
+      </c>
+      <c r="K82" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3494,18 +3743,21 @@
         <v>35</v>
       </c>
       <c r="F83" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G83" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J83" t="n">
+        <v>28</v>
+      </c>
+      <c r="K83" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3533,15 +3785,18 @@
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
+        <v>10</v>
+      </c>
+      <c r="K84" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3566,18 +3821,21 @@
         <v>19</v>
       </c>
       <c r="F85" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G85" t="n">
+        <v>7</v>
+      </c>
+      <c r="H85" t="n">
         <v>4</v>
       </c>
-      <c r="H85" t="n">
-        <v>14</v>
-      </c>
       <c r="I85" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
+        <v>22</v>
+      </c>
+      <c r="K85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3602,18 +3860,21 @@
         <v>9</v>
       </c>
       <c r="F86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
         <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J86" t="n">
+        <v>6</v>
+      </c>
+      <c r="K86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3638,18 +3899,21 @@
         <v>26</v>
       </c>
       <c r="F87" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G87" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H87" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I87" t="n">
         <v>11</v>
       </c>
       <c r="J87" t="n">
+        <v>24</v>
+      </c>
+      <c r="K87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3674,18 +3938,21 @@
         <v>67</v>
       </c>
       <c r="F88" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="G88" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="H88" t="n">
+        <v>23</v>
+      </c>
+      <c r="I88" t="n">
         <v>31</v>
       </c>
-      <c r="I88" t="n">
-        <v>24</v>
-      </c>
       <c r="J88" t="n">
+        <v>55</v>
+      </c>
+      <c r="K88" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3710,7 +3977,7 @@
         <v>7</v>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>3</v>
@@ -3719,9 +3986,12 @@
         <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
+        <v>3</v>
+      </c>
+      <c r="K89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3746,18 +4016,21 @@
         <v>31</v>
       </c>
       <c r="F90" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H90" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I90" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J90" t="n">
+        <v>24</v>
+      </c>
+      <c r="K90" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3782,18 +4055,21 @@
         <v>26</v>
       </c>
       <c r="F91" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H91" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I91" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
+        <v>25</v>
+      </c>
+      <c r="K91" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3818,18 +4094,21 @@
         <v>34</v>
       </c>
       <c r="F92" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H92" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
         <v>9</v>
       </c>
       <c r="J92" t="n">
+        <v>22</v>
+      </c>
+      <c r="K92" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3854,18 +4133,21 @@
         <v>45</v>
       </c>
       <c r="F93" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H93" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" t="n">
         <v>13</v>
       </c>
-      <c r="I93" t="n">
-        <v>21</v>
-      </c>
       <c r="J93" t="n">
+        <v>34</v>
+      </c>
+      <c r="K93" t="n">
         <v>13</v>
       </c>
     </row>
@@ -3890,18 +4172,21 @@
         <v>32</v>
       </c>
       <c r="F94" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G94" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I94" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J94" t="n">
+        <v>31</v>
+      </c>
+      <c r="K94" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3926,18 +4211,21 @@
         <v>30</v>
       </c>
       <c r="F95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G95" t="n">
         <v>6</v>
       </c>
       <c r="H95" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
+        <v>26</v>
+      </c>
+      <c r="K95" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3962,18 +4250,21 @@
         <v>21</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I96" t="n">
         <v>13</v>
       </c>
       <c r="J96" t="n">
+        <v>24</v>
+      </c>
+      <c r="K96" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3998,18 +4289,21 @@
         <v>25</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G97" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H97" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J97" t="n">
+        <v>20</v>
+      </c>
+      <c r="K97" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4034,18 +4328,21 @@
         <v>24</v>
       </c>
       <c r="F98" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I98" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J98" t="n">
+        <v>23</v>
+      </c>
+      <c r="K98" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4070,18 +4367,21 @@
         <v>45</v>
       </c>
       <c r="F99" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G99" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H99" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I99" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J99" t="n">
+        <v>36</v>
+      </c>
+      <c r="K99" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4106,18 +4406,21 @@
         <v>43</v>
       </c>
       <c r="F100" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G100" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H100" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I100" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J100" t="n">
+        <v>39</v>
+      </c>
+      <c r="K100" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4142,18 +4445,21 @@
         <v>29</v>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I101" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J101" t="n">
+        <v>32</v>
+      </c>
+      <c r="K101" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4178,18 +4484,21 @@
         <v>78</v>
       </c>
       <c r="F102" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G102" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H102" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I102" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J102" t="n">
+        <v>43</v>
+      </c>
+      <c r="K102" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4214,18 +4523,21 @@
         <v>22</v>
       </c>
       <c r="F103" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J103" t="n">
+        <v>23</v>
+      </c>
+      <c r="K103" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4250,18 +4562,21 @@
         <v>41</v>
       </c>
       <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>6</v>
+      </c>
+      <c r="H104" t="n">
+        <v>7</v>
+      </c>
+      <c r="I104" t="n">
         <v>14</v>
       </c>
-      <c r="G104" t="n">
-        <v>17</v>
-      </c>
-      <c r="H104" t="n">
-        <v>14</v>
-      </c>
-      <c r="I104" t="n">
-        <v>16</v>
-      </c>
       <c r="J104" t="n">
+        <v>30</v>
+      </c>
+      <c r="K104" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4286,18 +4601,21 @@
         <v>35</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H105" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I105" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J105" t="n">
+        <v>34</v>
+      </c>
+      <c r="K105" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4322,18 +4640,21 @@
         <v>32</v>
       </c>
       <c r="F106" t="n">
+        <v>4</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" t="n">
+        <v>8</v>
+      </c>
+      <c r="I106" t="n">
         <v>11</v>
       </c>
-      <c r="G106" t="n">
-        <v>16</v>
-      </c>
-      <c r="H106" t="n">
-        <v>18</v>
-      </c>
-      <c r="I106" t="n">
-        <v>8</v>
-      </c>
       <c r="J106" t="n">
+        <v>26</v>
+      </c>
+      <c r="K106" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4358,18 +4679,21 @@
         <v>48</v>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G107" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H107" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I107" t="n">
         <v>14</v>
       </c>
       <c r="J107" t="n">
+        <v>44</v>
+      </c>
+      <c r="K107" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4394,18 +4718,21 @@
         <v>30</v>
       </c>
       <c r="F108" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H108" t="n">
         <v>7</v>
       </c>
       <c r="I108" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J108" t="n">
+        <v>16</v>
+      </c>
+      <c r="K108" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4430,18 +4757,21 @@
         <v>55</v>
       </c>
       <c r="F109" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G109" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H109" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J109" t="n">
+        <v>35</v>
+      </c>
+      <c r="K109" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4466,18 +4796,21 @@
         <v>70</v>
       </c>
       <c r="F110" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G110" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H110" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I110" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J110" t="n">
+        <v>39</v>
+      </c>
+      <c r="K110" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4502,18 +4835,21 @@
         <v>31</v>
       </c>
       <c r="F111" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G111" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H111" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J111" t="n">
+        <v>22</v>
+      </c>
+      <c r="K111" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4538,18 +4874,21 @@
         <v>77</v>
       </c>
       <c r="F112" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H112" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="I112" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J112" t="n">
+        <v>67</v>
+      </c>
+      <c r="K112" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4574,18 +4913,21 @@
         <v>34</v>
       </c>
       <c r="F113" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G113" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I113" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J113" t="n">
+        <v>27</v>
+      </c>
+      <c r="K113" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4610,18 +4952,21 @@
         <v>37</v>
       </c>
       <c r="F114" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G114" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H114" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I114" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J114" t="n">
+        <v>21</v>
+      </c>
+      <c r="K114" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4646,18 +4991,21 @@
         <v>49</v>
       </c>
       <c r="F115" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="G115" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H115" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I115" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J115" t="n">
+        <v>35</v>
+      </c>
+      <c r="K115" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4682,18 +5030,21 @@
         <v>17</v>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G116" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I116" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J116" t="n">
+        <v>13</v>
+      </c>
+      <c r="K116" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4718,18 +5069,21 @@
         <v>16</v>
       </c>
       <c r="F117" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G117" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H117" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
         <v>7</v>
       </c>
       <c r="J117" t="n">
+        <v>12</v>
+      </c>
+      <c r="K117" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4757,15 +5111,18 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
         <v>7</v>
       </c>
-      <c r="J118" t="n">
+      <c r="K118" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4790,18 +5147,21 @@
         <v>36</v>
       </c>
       <c r="F119" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G119" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H119" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I119" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J119" t="n">
+        <v>25</v>
+      </c>
+      <c r="K119" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4826,18 +5186,21 @@
         <v>40</v>
       </c>
       <c r="F120" t="n">
+        <v>6</v>
+      </c>
+      <c r="G120" t="n">
+        <v>6</v>
+      </c>
+      <c r="H120" t="n">
+        <v>6</v>
+      </c>
+      <c r="I120" t="n">
         <v>16</v>
       </c>
-      <c r="G120" t="n">
-        <v>18</v>
-      </c>
-      <c r="H120" t="n">
-        <v>22</v>
-      </c>
-      <c r="I120" t="n">
-        <v>14</v>
-      </c>
       <c r="J120" t="n">
+        <v>36</v>
+      </c>
+      <c r="K120" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4862,18 +5225,21 @@
         <v>52</v>
       </c>
       <c r="F121" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G121" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H121" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J121" t="n">
+        <v>38</v>
+      </c>
+      <c r="K121" t="n">
         <v>16</v>
       </c>
     </row>
@@ -4898,18 +5264,21 @@
         <v>34</v>
       </c>
       <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="n">
+        <v>5</v>
+      </c>
+      <c r="H122" t="n">
         <v>9</v>
       </c>
-      <c r="G122" t="n">
-        <v>19</v>
-      </c>
-      <c r="H122" t="n">
-        <v>14</v>
-      </c>
       <c r="I122" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J122" t="n">
+        <v>32</v>
+      </c>
+      <c r="K122" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4934,18 +5303,21 @@
         <v>17</v>
       </c>
       <c r="F123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" t="n">
         <v>7</v>
       </c>
-      <c r="H123" t="n">
-        <v>8</v>
-      </c>
       <c r="I123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
+        <v>15</v>
+      </c>
+      <c r="K123" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4970,18 +5342,21 @@
         <v>133</v>
       </c>
       <c r="F124" t="n">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="G124" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="H124" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="I124" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J124" t="n">
+        <v>104</v>
+      </c>
+      <c r="K124" t="n">
         <v>18</v>
       </c>
     </row>
@@ -5006,18 +5381,21 @@
         <v>53</v>
       </c>
       <c r="F125" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H125" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I125" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J125" t="n">
+        <v>40</v>
+      </c>
+      <c r="K125" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5042,18 +5420,21 @@
         <v>59</v>
       </c>
       <c r="F126" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H126" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I126" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J126" t="n">
+        <v>52</v>
+      </c>
+      <c r="K126" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5078,18 +5459,21 @@
         <v>26</v>
       </c>
       <c r="F127" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G127" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H127" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I127" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J127" t="n">
+        <v>22</v>
+      </c>
+      <c r="K127" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5114,18 +5498,21 @@
         <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H128" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I128" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J128" t="n">
+        <v>33</v>
+      </c>
+      <c r="K128" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5150,18 +5537,21 @@
         <v>40</v>
       </c>
       <c r="F129" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G129" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H129" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I129" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J129" t="n">
+        <v>37</v>
+      </c>
+      <c r="K129" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5186,18 +5576,21 @@
         <v>47</v>
       </c>
       <c r="F130" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G130" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H130" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I130" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J130" t="n">
+        <v>37</v>
+      </c>
+      <c r="K130" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5222,18 +5615,21 @@
         <v>51</v>
       </c>
       <c r="F131" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G131" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H131" t="n">
+        <v>8</v>
+      </c>
+      <c r="I131" t="n">
         <v>12</v>
       </c>
-      <c r="I131" t="n">
-        <v>29</v>
-      </c>
       <c r="J131" t="n">
+        <v>41</v>
+      </c>
+      <c r="K131" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5258,18 +5654,21 @@
         <v>30</v>
       </c>
       <c r="F132" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H132" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I132" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J132" t="n">
+        <v>29</v>
+      </c>
+      <c r="K132" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5294,18 +5693,21 @@
         <v>66</v>
       </c>
       <c r="F133" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G133" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H133" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I133" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J133" t="n">
+        <v>52</v>
+      </c>
+      <c r="K133" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5330,18 +5732,21 @@
         <v>38</v>
       </c>
       <c r="F134" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G134" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" t="n">
         <v>18</v>
       </c>
-      <c r="H134" t="n">
-        <v>6</v>
-      </c>
-      <c r="I134" t="n">
-        <v>14</v>
-      </c>
       <c r="J134" t="n">
+        <v>20</v>
+      </c>
+      <c r="K134" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5366,18 +5771,21 @@
         <v>14</v>
       </c>
       <c r="F135" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H135" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I135" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J135" t="n">
+        <v>14</v>
+      </c>
+      <c r="K135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5402,18 +5810,21 @@
         <v>50</v>
       </c>
       <c r="F136" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G136" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H136" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I136" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J136" t="n">
+        <v>38</v>
+      </c>
+      <c r="K136" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5438,18 +5849,21 @@
         <v>31</v>
       </c>
       <c r="F137" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G137" t="n">
+        <v>9</v>
+      </c>
+      <c r="H137" t="n">
         <v>6</v>
       </c>
-      <c r="H137" t="n">
-        <v>12</v>
-      </c>
       <c r="I137" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J137" t="n">
+        <v>23</v>
+      </c>
+      <c r="K137" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5474,18 +5888,21 @@
         <v>30</v>
       </c>
       <c r="F138" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G138" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H138" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I138" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J138" t="n">
+        <v>18</v>
+      </c>
+      <c r="K138" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5510,18 +5927,21 @@
         <v>29</v>
       </c>
       <c r="F139" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G139" t="n">
+        <v>5</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
         <v>14</v>
       </c>
-      <c r="H139" t="n">
-        <v>11</v>
-      </c>
-      <c r="I139" t="n">
-        <v>10</v>
-      </c>
       <c r="J139" t="n">
+        <v>21</v>
+      </c>
+      <c r="K139" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5546,18 +5966,21 @@
         <v>36</v>
       </c>
       <c r="F140" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G140" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H140" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I140" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J140" t="n">
+        <v>28</v>
+      </c>
+      <c r="K140" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5582,18 +6005,21 @@
         <v>145</v>
       </c>
       <c r="F141" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="G141" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="H141" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="I141" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J141" t="n">
+        <v>99</v>
+      </c>
+      <c r="K141" t="n">
         <v>30</v>
       </c>
     </row>
@@ -5618,18 +6044,21 @@
         <v>40</v>
       </c>
       <c r="F142" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G142" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H142" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I142" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J142" t="n">
+        <v>29</v>
+      </c>
+      <c r="K142" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5654,18 +6083,21 @@
         <v>55</v>
       </c>
       <c r="F143" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G143" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H143" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I143" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J143" t="n">
+        <v>42</v>
+      </c>
+      <c r="K143" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5690,18 +6122,21 @@
         <v>45</v>
       </c>
       <c r="F144" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H144" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I144" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J144" t="n">
+        <v>39</v>
+      </c>
+      <c r="K144" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5726,18 +6161,21 @@
         <v>39</v>
       </c>
       <c r="F145" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H145" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I145" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J145" t="n">
+        <v>36</v>
+      </c>
+      <c r="K145" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5762,18 +6200,21 @@
         <v>29</v>
       </c>
       <c r="F146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H146" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I146" t="n">
         <v>12</v>
       </c>
       <c r="J146" t="n">
+        <v>20</v>
+      </c>
+      <c r="K146" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5798,18 +6239,21 @@
         <v>12</v>
       </c>
       <c r="F147" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G147" t="n">
         <v>4</v>
       </c>
       <c r="H147" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J147" t="n">
+        <v>14</v>
+      </c>
+      <c r="K147" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5834,18 +6278,21 @@
         <v>18</v>
       </c>
       <c r="F148" t="n">
+        <v>3</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" t="n">
+        <v>2</v>
+      </c>
+      <c r="I148" t="n">
         <v>8</v>
       </c>
-      <c r="G148" t="n">
-        <v>10</v>
-      </c>
-      <c r="H148" t="n">
-        <v>6</v>
-      </c>
-      <c r="I148" t="n">
-        <v>6</v>
-      </c>
       <c r="J148" t="n">
+        <v>12</v>
+      </c>
+      <c r="K148" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5870,18 +6317,21 @@
         <v>40</v>
       </c>
       <c r="F149" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H149" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I149" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J149" t="n">
+        <v>35</v>
+      </c>
+      <c r="K149" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5906,18 +6356,21 @@
         <v>24</v>
       </c>
       <c r="F150" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H150" t="n">
+        <v>5</v>
+      </c>
+      <c r="I150" t="n">
         <v>13</v>
       </c>
-      <c r="I150" t="n">
-        <v>9</v>
-      </c>
       <c r="J150" t="n">
+        <v>22</v>
+      </c>
+      <c r="K150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5942,18 +6395,21 @@
         <v>36</v>
       </c>
       <c r="F151" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G151" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H151" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I151" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J151" t="n">
+        <v>27</v>
+      </c>
+      <c r="K151" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5978,18 +6434,21 @@
         <v>39</v>
       </c>
       <c r="F152" t="n">
+        <v>5</v>
+      </c>
+      <c r="G152" t="n">
+        <v>5</v>
+      </c>
+      <c r="H152" t="n">
+        <v>4</v>
+      </c>
+      <c r="I152" t="n">
         <v>14</v>
       </c>
-      <c r="G152" t="n">
-        <v>14</v>
-      </c>
-      <c r="H152" t="n">
-        <v>12</v>
-      </c>
-      <c r="I152" t="n">
-        <v>20</v>
-      </c>
       <c r="J152" t="n">
+        <v>32</v>
+      </c>
+      <c r="K152" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6014,18 +6473,21 @@
         <v>40</v>
       </c>
       <c r="F153" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G153" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H153" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I153" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J153" t="n">
+        <v>32</v>
+      </c>
+      <c r="K153" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6053,15 +6515,18 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
       </c>
       <c r="I154" t="n">
+        <v>3</v>
+      </c>
+      <c r="J154" t="n">
         <v>2</v>
       </c>
-      <c r="J154" t="n">
+      <c r="K154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6086,18 +6551,21 @@
         <v>36</v>
       </c>
       <c r="F155" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G155" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H155" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I155" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J155" t="n">
+        <v>27</v>
+      </c>
+      <c r="K155" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6122,18 +6590,21 @@
         <v>32</v>
       </c>
       <c r="F156" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" t="n">
+        <v>2</v>
+      </c>
+      <c r="H156" t="n">
         <v>4</v>
       </c>
-      <c r="G156" t="n">
-        <v>13</v>
-      </c>
-      <c r="H156" t="n">
-        <v>14</v>
-      </c>
       <c r="I156" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J156" t="n">
+        <v>33</v>
+      </c>
+      <c r="K156" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6158,18 +6629,21 @@
         <v>29</v>
       </c>
       <c r="F157" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G157" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H157" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I157" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J157" t="n">
+        <v>19</v>
+      </c>
+      <c r="K157" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6194,18 +6668,21 @@
         <v>44</v>
       </c>
       <c r="F158" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G158" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H158" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I158" t="n">
         <v>11</v>
       </c>
       <c r="J158" t="n">
+        <v>29</v>
+      </c>
+      <c r="K158" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6230,18 +6707,21 @@
         <v>32</v>
       </c>
       <c r="F159" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G159" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H159" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I159" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J159" t="n">
+        <v>20</v>
+      </c>
+      <c r="K159" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6266,18 +6746,21 @@
         <v>31</v>
       </c>
       <c r="F160" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H160" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I160" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J160" t="n">
+        <v>29</v>
+      </c>
+      <c r="K160" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6302,18 +6785,21 @@
         <v>19</v>
       </c>
       <c r="F161" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H161" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I161" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J161" t="n">
+        <v>17</v>
+      </c>
+      <c r="K161" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6338,18 +6824,21 @@
         <v>55</v>
       </c>
       <c r="F162" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G162" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H162" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I162" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J162" t="n">
+        <v>47</v>
+      </c>
+      <c r="K162" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6374,18 +6863,21 @@
         <v>34</v>
       </c>
       <c r="F163" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G163" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H163" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I163" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J163" t="n">
+        <v>23</v>
+      </c>
+      <c r="K163" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6410,18 +6902,21 @@
         <v>21</v>
       </c>
       <c r="F164" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H164" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I164" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J164" t="n">
+        <v>20</v>
+      </c>
+      <c r="K164" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6446,18 +6941,21 @@
         <v>33</v>
       </c>
       <c r="F165" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G165" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H165" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I165" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J165" t="n">
+        <v>30</v>
+      </c>
+      <c r="K165" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6488,12 +6986,15 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6518,18 +7019,21 @@
         <v>95</v>
       </c>
       <c r="F167" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G167" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H167" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I167" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="J167" t="n">
+        <v>75</v>
+      </c>
+      <c r="K167" t="n">
         <v>25</v>
       </c>
     </row>
@@ -6554,18 +7058,21 @@
         <v>62</v>
       </c>
       <c r="F168" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G168" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H168" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I168" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J168" t="n">
+        <v>43</v>
+      </c>
+      <c r="K168" t="n">
         <v>17</v>
       </c>
     </row>
@@ -6590,18 +7097,21 @@
         <v>34</v>
       </c>
       <c r="F169" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H169" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I169" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J169" t="n">
+        <v>34</v>
+      </c>
+      <c r="K169" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6626,18 +7136,21 @@
         <v>44</v>
       </c>
       <c r="F170" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G170" t="n">
+        <v>10</v>
+      </c>
+      <c r="H170" t="n">
+        <v>3</v>
+      </c>
+      <c r="I170" t="n">
         <v>21</v>
       </c>
-      <c r="H170" t="n">
-        <v>17</v>
-      </c>
-      <c r="I170" t="n">
-        <v>15</v>
-      </c>
       <c r="J170" t="n">
+        <v>32</v>
+      </c>
+      <c r="K170" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6662,18 +7175,21 @@
         <v>68</v>
       </c>
       <c r="F171" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G171" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H171" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I171" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J171" t="n">
+        <v>48</v>
+      </c>
+      <c r="K171" t="n">
         <v>16</v>
       </c>
     </row>
@@ -6698,18 +7214,21 @@
         <v>10</v>
       </c>
       <c r="F172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
         <v>1</v>
       </c>
-      <c r="H172" t="n">
-        <v>7</v>
-      </c>
-      <c r="I172" t="n">
-        <v>3</v>
-      </c>
       <c r="J172" t="n">
+        <v>10</v>
+      </c>
+      <c r="K172" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6734,18 +7253,21 @@
         <v>248</v>
       </c>
       <c r="F173" t="n">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="G173" t="n">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="H173" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="I173" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="J173" t="n">
+        <v>178</v>
+      </c>
+      <c r="K173" t="n">
         <v>38</v>
       </c>
     </row>
@@ -6770,18 +7292,21 @@
         <v>47</v>
       </c>
       <c r="F174" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G174" t="n">
+        <v>7</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2</v>
+      </c>
+      <c r="I174" t="n">
         <v>22</v>
       </c>
-      <c r="H174" t="n">
-        <v>17</v>
-      </c>
-      <c r="I174" t="n">
-        <v>18</v>
-      </c>
       <c r="J174" t="n">
+        <v>35</v>
+      </c>
+      <c r="K174" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6806,18 +7331,21 @@
         <v>35</v>
       </c>
       <c r="F175" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G175" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H175" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I175" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J175" t="n">
+        <v>32</v>
+      </c>
+      <c r="K175" t="n">
         <v>18</v>
       </c>
     </row>
@@ -6842,18 +7370,21 @@
         <v>45</v>
       </c>
       <c r="F176" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G176" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H176" t="n">
+        <v>4</v>
+      </c>
+      <c r="I176" t="n">
         <v>17</v>
       </c>
-      <c r="I176" t="n">
-        <v>31</v>
-      </c>
       <c r="J176" t="n">
+        <v>48</v>
+      </c>
+      <c r="K176" t="n">
         <v>7</v>
       </c>
     </row>
@@ -6878,18 +7409,21 @@
         <v>43</v>
       </c>
       <c r="F177" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G177" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H177" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I177" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J177" t="n">
+        <v>32</v>
+      </c>
+      <c r="K177" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6914,18 +7448,21 @@
         <v>35</v>
       </c>
       <c r="F178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I178" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J178" t="n">
+        <v>29</v>
+      </c>
+      <c r="K178" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6950,18 +7487,21 @@
         <v>32</v>
       </c>
       <c r="F179" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I179" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J179" t="n">
+        <v>25</v>
+      </c>
+      <c r="K179" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6986,18 +7526,21 @@
         <v>47</v>
       </c>
       <c r="F180" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H180" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I180" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J180" t="n">
+        <v>30</v>
+      </c>
+      <c r="K180" t="n">
         <v>13</v>
       </c>
     </row>
@@ -7022,18 +7565,21 @@
         <v>36</v>
       </c>
       <c r="F181" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H181" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I181" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J181" t="n">
+        <v>26</v>
+      </c>
+      <c r="K181" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7058,18 +7604,21 @@
         <v>28</v>
       </c>
       <c r="F182" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G182" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H182" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I182" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J182" t="n">
+        <v>26</v>
+      </c>
+      <c r="K182" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7094,18 +7643,21 @@
         <v>27</v>
       </c>
       <c r="F183" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H183" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I183" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J183" t="n">
+        <v>18</v>
+      </c>
+      <c r="K183" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7130,18 +7682,21 @@
         <v>17</v>
       </c>
       <c r="F184" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H184" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I184" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J184" t="n">
+        <v>16</v>
+      </c>
+      <c r="K184" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7166,18 +7721,21 @@
         <v>23</v>
       </c>
       <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>3</v>
+      </c>
+      <c r="H185" t="n">
+        <v>1</v>
+      </c>
+      <c r="I185" t="n">
         <v>4</v>
       </c>
-      <c r="G185" t="n">
-        <v>4</v>
-      </c>
-      <c r="H185" t="n">
-        <v>9</v>
-      </c>
-      <c r="I185" t="n">
-        <v>12</v>
-      </c>
       <c r="J185" t="n">
+        <v>21</v>
+      </c>
+      <c r="K185" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7202,18 +7760,21 @@
         <v>17</v>
       </c>
       <c r="F186" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H186" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I186" t="n">
         <v>10</v>
       </c>
       <c r="J186" t="n">
+        <v>15</v>
+      </c>
+      <c r="K186" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7238,18 +7799,21 @@
         <v>19</v>
       </c>
       <c r="F187" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G187" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I187" t="n">
         <v>11</v>
       </c>
       <c r="J187" t="n">
+        <v>14</v>
+      </c>
+      <c r="K187" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7274,18 +7838,21 @@
         <v>21</v>
       </c>
       <c r="F188" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G188" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H188" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I188" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J188" t="n">
+        <v>19</v>
+      </c>
+      <c r="K188" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7310,18 +7877,21 @@
         <v>22</v>
       </c>
       <c r="F189" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G189" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H189" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I189" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J189" t="n">
+        <v>22</v>
+      </c>
+      <c r="K189" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7346,18 +7916,21 @@
         <v>48</v>
       </c>
       <c r="F190" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G190" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H190" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I190" t="n">
         <v>15</v>
       </c>
       <c r="J190" t="n">
+        <v>37</v>
+      </c>
+      <c r="K190" t="n">
         <v>8</v>
       </c>
     </row>
@@ -7382,18 +7955,21 @@
         <v>47</v>
       </c>
       <c r="F191" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G191" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H191" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I191" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J191" t="n">
+        <v>26</v>
+      </c>
+      <c r="K191" t="n">
         <v>22</v>
       </c>
     </row>
@@ -7418,18 +7994,21 @@
         <v>41</v>
       </c>
       <c r="F192" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G192" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H192" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I192" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J192" t="n">
+        <v>28</v>
+      </c>
+      <c r="K192" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7454,18 +8033,21 @@
         <v>56</v>
       </c>
       <c r="F193" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G193" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H193" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I193" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J193" t="n">
+        <v>52</v>
+      </c>
+      <c r="K193" t="n">
         <v>16</v>
       </c>
     </row>
@@ -7490,18 +8072,21 @@
         <v>42</v>
       </c>
       <c r="F194" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G194" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H194" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I194" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J194" t="n">
+        <v>37</v>
+      </c>
+      <c r="K194" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7526,18 +8111,21 @@
         <v>17</v>
       </c>
       <c r="F195" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G195" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H195" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I195" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J195" t="n">
+        <v>16</v>
+      </c>
+      <c r="K195" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7562,18 +8150,21 @@
         <v>39</v>
       </c>
       <c r="F196" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G196" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H196" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I196" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J196" t="n">
+        <v>33</v>
+      </c>
+      <c r="K196" t="n">
         <v>14</v>
       </c>
     </row>
@@ -7598,18 +8189,21 @@
         <v>40</v>
       </c>
       <c r="F197" t="n">
+        <v>6</v>
+      </c>
+      <c r="G197" t="n">
+        <v>6</v>
+      </c>
+      <c r="H197" t="n">
+        <v>9</v>
+      </c>
+      <c r="I197" t="n">
         <v>18</v>
       </c>
-      <c r="G197" t="n">
-        <v>21</v>
-      </c>
-      <c r="H197" t="n">
-        <v>19</v>
-      </c>
-      <c r="I197" t="n">
-        <v>13</v>
-      </c>
       <c r="J197" t="n">
+        <v>32</v>
+      </c>
+      <c r="K197" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7634,23 +8228,26 @@
         <v>112</v>
       </c>
       <c r="F198" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G198" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="H198" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="I198" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J198" t="n">
+        <v>83</v>
+      </c>
+      <c r="K198" t="n">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/riobamba-censo-data/shp/plataforma_enie.xlsx
+++ b/riobamba-censo-data/shp/plataforma_enie.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$AG$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$AI$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG198"/>
+  <dimension ref="A1:AI198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,8 @@
     <col width="24" customWidth="1" min="31" max="31"/>
     <col width="24" customWidth="1" min="32" max="32"/>
     <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="24" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,6 +696,16 @@
           <t>iso_nom_22</t>
         </is>
       </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>sal_nom_1</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>sal_nom_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -835,6 +847,12 @@
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -972,6 +990,8 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1109,6 +1129,12 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1206,6 +1232,8 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1303,6 +1331,8 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1388,6 +1418,8 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1481,6 +1513,8 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1618,6 +1652,8 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1747,6 +1783,8 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1880,6 +1918,8 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2009,6 +2049,8 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2146,6 +2188,8 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2295,6 +2339,8 @@
           <t>iso_087_parada_400m_PARADA_BUS_087_Parada_087_-_Lineas_16</t>
         </is>
       </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2440,6 +2486,8 @@
         </is>
       </c>
       <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2577,6 +2625,8 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2726,6 +2776,8 @@
           <t>iso_046_parada_400m_PARADA_BUS_046_Parada_046_-_Lineas_07_10</t>
         </is>
       </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2807,6 +2859,8 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2880,6 +2934,8 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2965,6 +3021,8 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3042,6 +3100,8 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3127,6 +3187,8 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3264,6 +3326,8 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3397,6 +3461,8 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3534,6 +3600,8 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3619,6 +3687,8 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3720,6 +3790,8 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3821,6 +3893,8 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3906,6 +3980,8 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3987,6 +4063,8 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4068,6 +4146,8 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4149,6 +4229,8 @@
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4218,6 +4300,8 @@
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4303,6 +4387,8 @@
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4416,6 +4502,8 @@
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4505,6 +4593,8 @@
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4598,6 +4688,12 @@
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4687,6 +4783,12 @@
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4780,6 +4882,8 @@
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4853,6 +4957,8 @@
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4934,6 +5040,8 @@
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5015,6 +5123,8 @@
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5088,6 +5198,8 @@
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5165,6 +5277,8 @@
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5242,6 +5356,8 @@
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5311,6 +5427,8 @@
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5400,6 +5518,8 @@
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5485,6 +5605,8 @@
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5586,6 +5708,12 @@
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5695,6 +5823,12 @@
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5804,6 +5938,12 @@
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5909,6 +6049,12 @@
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6022,6 +6168,12 @@
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6151,6 +6303,12 @@
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6228,6 +6386,8 @@
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6313,6 +6473,8 @@
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6398,6 +6560,8 @@
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6483,6 +6647,8 @@
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6568,6 +6734,8 @@
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6649,6 +6817,8 @@
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6730,6 +6900,8 @@
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6811,6 +6983,8 @@
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6888,6 +7062,8 @@
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6969,6 +7145,8 @@
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7050,6 +7228,8 @@
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7131,6 +7311,8 @@
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7204,6 +7386,8 @@
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7281,6 +7465,8 @@
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7366,6 +7552,8 @@
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7451,6 +7639,8 @@
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7536,6 +7726,8 @@
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7625,6 +7817,8 @@
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7730,6 +7924,8 @@
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7823,6 +8019,8 @@
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7884,6 +8082,8 @@
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7977,6 +8177,12 @@
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8066,6 +8272,8 @@
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8159,6 +8367,8 @@
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8248,6 +8458,8 @@
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8341,6 +8553,8 @@
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8418,6 +8632,12 @@
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8495,6 +8715,8 @@
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8576,6 +8798,8 @@
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8649,6 +8873,8 @@
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8726,6 +8952,8 @@
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8803,6 +9031,8 @@
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8876,6 +9106,8 @@
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8937,6 +9169,8 @@
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8998,6 +9232,8 @@
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9083,6 +9319,16 @@
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9164,6 +9410,16 @@
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9245,6 +9501,16 @@
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9322,6 +9588,16 @@
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9403,6 +9679,16 @@
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9484,6 +9770,12 @@
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9565,6 +9857,12 @@
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9642,6 +9940,12 @@
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9723,6 +10027,8 @@
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9812,6 +10118,8 @@
       <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9917,6 +10225,12 @@
       <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10010,6 +10324,12 @@
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10095,6 +10415,12 @@
       <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10196,6 +10522,12 @@
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10301,6 +10633,12 @@
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10398,6 +10736,12 @@
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10491,6 +10835,8 @@
       <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10552,6 +10898,8 @@
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10645,6 +10993,8 @@
       <c r="AE108" t="inlineStr"/>
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10730,6 +11080,8 @@
       <c r="AE109" t="inlineStr"/>
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10823,6 +11175,8 @@
       <c r="AE110" t="inlineStr"/>
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10888,6 +11242,8 @@
       <c r="AE111" t="inlineStr"/>
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10949,6 +11305,8 @@
       <c r="AE112" t="inlineStr"/>
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11010,6 +11368,8 @@
       <c r="AE113" t="inlineStr"/>
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11095,6 +11455,8 @@
       <c r="AE114" t="inlineStr"/>
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11180,6 +11542,8 @@
       <c r="AE115" t="inlineStr"/>
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11265,6 +11629,8 @@
       <c r="AE116" t="inlineStr"/>
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11350,6 +11716,8 @@
       <c r="AE117" t="inlineStr"/>
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11427,6 +11795,8 @@
       <c r="AE118" t="inlineStr"/>
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11540,6 +11910,12 @@
       <c r="AE119" t="inlineStr"/>
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11641,6 +12017,12 @@
       <c r="AE120" t="inlineStr"/>
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11750,6 +12132,12 @@
       <c r="AE121" t="inlineStr"/>
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11851,6 +12239,12 @@
       <c r="AE122" t="inlineStr"/>
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11920,6 +12314,8 @@
       <c r="AE123" t="inlineStr"/>
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11989,6 +12385,8 @@
       <c r="AE124" t="inlineStr"/>
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12066,6 +12464,8 @@
       <c r="AE125" t="inlineStr"/>
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12171,6 +12571,12 @@
       <c r="AE126" t="inlineStr"/>
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -12272,6 +12678,12 @@
       <c r="AE127" t="inlineStr"/>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -12365,6 +12777,12 @@
       <c r="AE128" t="inlineStr"/>
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -12446,6 +12864,12 @@
       <c r="AE129" t="inlineStr"/>
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12531,6 +12955,12 @@
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12652,6 +13082,12 @@
       <c r="AE131" t="inlineStr"/>
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12789,6 +13225,12 @@
       <c r="AE132" t="inlineStr"/>
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12926,6 +13368,12 @@
       <c r="AE133" t="inlineStr"/>
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13059,6 +13507,12 @@
       <c r="AE134" t="inlineStr"/>
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13140,6 +13594,12 @@
       <c r="AE135" t="inlineStr"/>
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13217,6 +13677,12 @@
       <c r="AE136" t="inlineStr"/>
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13306,6 +13772,16 @@
       <c r="AE137" t="inlineStr"/>
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13391,6 +13867,16 @@
       <c r="AE138" t="inlineStr"/>
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -13476,6 +13962,12 @@
       <c r="AE139" t="inlineStr"/>
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -13561,6 +14053,12 @@
       <c r="AE140" t="inlineStr"/>
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13638,6 +14136,8 @@
       <c r="AE141" t="inlineStr"/>
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13751,6 +14251,12 @@
       <c r="AE142" t="inlineStr"/>
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13864,6 +14370,12 @@
       <c r="AE143" t="inlineStr"/>
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13981,6 +14493,12 @@
       <c r="AE144" t="inlineStr"/>
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14042,6 +14560,8 @@
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14111,6 +14631,8 @@
       <c r="AE146" t="inlineStr"/>
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -14176,6 +14698,8 @@
       <c r="AE147" t="inlineStr"/>
       <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -14241,6 +14765,8 @@
       <c r="AE148" t="inlineStr"/>
       <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -14310,6 +14836,8 @@
       <c r="AE149" t="inlineStr"/>
       <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -14387,6 +14915,8 @@
       <c r="AE150" t="inlineStr"/>
       <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -14452,6 +14982,8 @@
       <c r="AE151" t="inlineStr"/>
       <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14537,6 +15069,12 @@
       <c r="AE152" t="inlineStr"/>
       <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14630,6 +15168,12 @@
       <c r="AE153" t="inlineStr"/>
       <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14739,6 +15283,12 @@
       <c r="AE154" t="inlineStr"/>
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14844,6 +15394,12 @@
       <c r="AE155" t="inlineStr"/>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14949,6 +15505,12 @@
       <c r="AE156" t="inlineStr"/>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15034,6 +15596,16 @@
       <c r="AE157" t="inlineStr"/>
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15115,6 +15687,12 @@
       <c r="AE158" t="inlineStr"/>
       <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15196,6 +15774,12 @@
       <c r="AE159" t="inlineStr"/>
       <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15277,6 +15861,12 @@
       <c r="AE160" t="inlineStr"/>
       <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15366,6 +15956,12 @@
       <c r="AE161" t="inlineStr"/>
       <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15443,6 +16039,16 @@
       <c r="AE162" t="inlineStr"/>
       <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -15520,6 +16126,16 @@
       <c r="AE163" t="inlineStr"/>
       <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15593,6 +16209,16 @@
       <c r="AE164" t="inlineStr"/>
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15670,6 +16296,12 @@
       <c r="AE165" t="inlineStr"/>
       <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15743,6 +16375,16 @@
       <c r="AE166" t="inlineStr"/>
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15824,6 +16466,16 @@
       <c r="AE167" t="inlineStr"/>
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>iso_001_barrial_060101003003002_Centro_de_embarazas</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15901,6 +16553,12 @@
       <c r="AE168" t="inlineStr"/>
       <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -15982,6 +16640,12 @@
       <c r="AE169" t="inlineStr"/>
       <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -16071,6 +16735,12 @@
       <c r="AE170" t="inlineStr"/>
       <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -16168,6 +16838,12 @@
       <c r="AE171" t="inlineStr"/>
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -16233,6 +16909,8 @@
       <c r="AE172" t="inlineStr"/>
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -16294,6 +16972,8 @@
       <c r="AE173" t="inlineStr"/>
       <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -16403,6 +17083,12 @@
       <c r="AE174" t="inlineStr"/>
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -16516,6 +17202,12 @@
       <c r="AE175" t="inlineStr"/>
       <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -16637,6 +17329,12 @@
       <c r="AE176" t="inlineStr"/>
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -16750,6 +17448,12 @@
       <c r="AE177" t="inlineStr"/>
       <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -16855,6 +17559,12 @@
       <c r="AE178" t="inlineStr"/>
       <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -16976,6 +17686,12 @@
       <c r="AE179" t="inlineStr"/>
       <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -17109,6 +17825,12 @@
       <c r="AE180" t="inlineStr"/>
       <c r="AF180" t="inlineStr"/>
       <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -17242,6 +17964,12 @@
       <c r="AE181" t="inlineStr"/>
       <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -17379,6 +18107,8 @@
       <c r="AE182" t="inlineStr"/>
       <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -17496,6 +18226,12 @@
       <c r="AE183" t="inlineStr"/>
       <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -17609,6 +18345,12 @@
       <c r="AE184" t="inlineStr"/>
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17726,6 +18468,12 @@
       <c r="AE185" t="inlineStr"/>
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17851,6 +18599,12 @@
       <c r="AE186" t="inlineStr"/>
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -17912,6 +18666,8 @@
       <c r="AE187" t="inlineStr"/>
       <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17973,6 +18729,8 @@
       <c r="AE188" t="inlineStr"/>
       <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -18082,6 +18840,12 @@
       <c r="AE189" t="inlineStr"/>
       <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -18203,6 +18967,12 @@
       <c r="AE190" t="inlineStr"/>
       <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -18324,6 +19094,12 @@
       <c r="AE191" t="inlineStr"/>
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -18453,6 +19229,8 @@
       <c r="AE192" t="inlineStr"/>
       <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -18578,6 +19356,8 @@
       <c r="AE193" t="inlineStr"/>
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -18691,6 +19471,8 @@
       <c r="AE194" t="inlineStr"/>
       <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -18816,6 +19598,12 @@
       <c r="AE195" t="inlineStr"/>
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -18933,6 +19721,12 @@
       <c r="AE196" t="inlineStr"/>
       <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>iso_002_zonal_060101003003002_Subcentro_de_Salud_Municipal</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -19002,6 +19796,8 @@
       <c r="AE197" t="inlineStr"/>
       <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -19063,9 +19859,11 @@
       <c r="AE198" t="inlineStr"/>
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1"/>
+  <autoFilter ref="A1:AI1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>